--- a/data/data/ICICI Prudential Mutual Fund/ICICI PRUDENTIAL SILVER ETF.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI PRUDENTIAL SILVER ETF.xlsx
@@ -1,26 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28429"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\mumchfnp01\RatingFinance\Factseet Mandates\ICICI PRUDENTIAL FACTSHEET\2025\Feb\Portfolio stage 8\Riskometer updated Portfolio\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48726CF3-F8AB-4570-AF1A-6D0CEE71BF29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="120" windowWidth="14940" windowHeight="9225" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="SILVER" sheetId="2" r:id="rId1"/>
+    <sheet name="SILVER" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="25">
   <si>
     <t>ICICI Prudential Mutual Fund</t>
   </si>
@@ -28,13 +22,13 @@
     <t>ICICI PRUDENTIAL SILVER ETF</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
   </si>
   <si>
-    <t>ISIN</t>
+    <t>	ISIN</t>
   </si>
   <si>
     <t>Industry/Rating</t>
@@ -73,10 +67,10 @@
     <t>Total Net Assets</t>
   </si>
   <si>
-    <t>^ - Physical Silver.</t>
-  </si>
-  <si>
-    <t>Aggregate value of investments made by other schemes of ICICI Prudential Mutual Fund are amounting to Rs. 169311.0  Lakh.</t>
+    <t>^ - Physical Silver</t>
+  </si>
+  <si>
+    <t>Aggregate value of investments made by other schemes of ICICI Prudential Mutual Fund are amounting to Rs. 206144.37  Lakh.</t>
   </si>
   <si>
     <t>For the Instrument/security whose final ISIN is yet to be assigned, disclosure of ISIN has been made as per the details provided by external agencies.</t>
@@ -85,7 +79,7 @@
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -95,25 +89,18 @@
   </si>
   <si>
     <t>Benchmark Riskometer</t>
-  </si>
-  <si>
-    <t>Benchmark name - LBMA AM fixing Prices (Domestic Price of Silver) (Benchmark)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="7">
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="##0.00"/>
-    <numFmt numFmtId="165" formatCode="##0.00%"/>
-    <numFmt numFmtId="166" formatCode="##0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="3">
+    <numFmt numFmtId="177" formatCode="##0.00"/>
+    <numFmt numFmtId="178" formatCode="##0.00%"/>
+    <numFmt numFmtId="179" formatCode="##0"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -138,7 +125,7 @@
     </font>
     <font>
       <b/>
-      <u/>
+      <u val="single"/>
       <sz val="8.5"/>
       <name val="Verdana"/>
       <family val="2"/>
@@ -156,16 +143,10 @@
       <name val="Verdana"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="5">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -206,7 +187,6 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -215,7 +195,6 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -226,7 +205,6 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -235,7 +213,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -244,103 +221,195 @@
       </right>
       <top/>
       <bottom/>
-      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
+      <protection/>
+    </xf>
+    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection/>
+    </xf>
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
-    <cellStyle name="Comma" xfId="4" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
-    <cellStyle name="Comma [0]" xfId="5" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
-    <cellStyle name="Currency" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
-    <cellStyle name="Currency [0]" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Normal" xfId="0"/>
+    <cellStyle name="Percent" xfId="15"/>
+    <cellStyle name="Currency" xfId="16"/>
+    <cellStyle name="Currency [0]" xfId="17"/>
+    <cellStyle name="Comma" xfId="18"/>
+    <cellStyle name="Comma [0]" xfId="19"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -356,19 +425,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="1" name="Picture 1" descr="Picture"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:blip r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -378,9 +441,7 @@
           <a:off x="666750" y="4972050"/>
           <a:ext cx="2771775" cy="1905000"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
+        <a:prstGeom prst="rect"/>
         <a:ln w="9525" cmpd="sng">
           <a:noFill/>
         </a:ln>
@@ -403,19 +464,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="2" name="Picture 1" descr="Picture"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:blip r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -425,9 +480,7 @@
           <a:off x="666750" y="7829550"/>
           <a:ext cx="2771775" cy="1905000"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
+        <a:prstGeom prst="rect"/>
         <a:ln w="9525" cmpd="sng">
           <a:noFill/>
         </a:ln>
@@ -757,36 +810,36 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J38"/>
-  <sheetFormatPr defaultColWidth="10" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <dimension ref="B1:J37"/>
+  <sheetFormatPr defaultColWidth="10" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="10" style="23" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="41.5703125" style="23" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="6.5703125" style="23" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="19.7109375" style="23" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="10.85546875" style="23" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="38.7109375" style="23" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="11.7109375" style="23" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="27.140625" style="23" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="29.7109375" style="23" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="26.7109375" style="23" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="1" max="1" customWidth="true" style="20" width="10.0" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="20" width="41.57142857142857" collapsed="true"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="20" width="6.571428571428571" collapsed="true"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="20" width="19.714285714285715" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="20" width="10.857142857142858" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="20" width="38.714285714285715" collapsed="true"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="20" width="11.714285714285714" collapsed="true"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="20" width="27.142857142857142" collapsed="true"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="20" width="29.714285714285715" collapsed="true"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="20" width="26.714285714285715" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B1" s="3" t="s">
+    <row r="1" spans="2:10" ht="15" customHeight="1">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-    </row>
-    <row r="2" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+    </row>
+    <row r="2" spans="2:10" ht="15" customHeight="1">
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
@@ -799,268 +852,263 @@
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="1" t="s">
+    <row r="3" spans="2:10" ht="15" customHeight="1">
+      <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-    </row>
-    <row r="4" spans="2:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B4" s="7" t="s">
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+    </row>
+    <row r="4" spans="2:9" ht="10.5">
+      <c r="B4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="G4" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="H4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="I4" s="6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="10" t="s">
+    <row r="5" spans="2:9" ht="15" customHeight="1">
+      <c r="B5" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="12">
-        <v>425389.59</v>
-      </c>
-      <c r="G5" s="13">
-        <v>0.9766412268004</v>
-      </c>
-      <c r="H5" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="I5" s="14" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="15" t="s">
+      <c r="C5" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="9">
+        <v>521062.74</v>
+      </c>
+      <c r="G5" s="10">
+        <v>0.9769947995493</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" ht="15" customHeight="1">
+      <c r="B6" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16" t="s">
+      <c r="C6" s="13"/>
+      <c r="D6" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="17">
-        <v>456446.35810000001</v>
-      </c>
-      <c r="F6" s="18">
-        <v>425389.59</v>
-      </c>
-      <c r="G6" s="19">
-        <v>0.9766412268004</v>
-      </c>
-      <c r="H6" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="I6" s="14" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="I7" s="14" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="10" t="s">
+      <c r="E6" s="14">
+        <v>535357.1544</v>
+      </c>
+      <c r="F6" s="15">
+        <v>521062.74</v>
+      </c>
+      <c r="G6" s="16">
+        <v>0.9769947995493</v>
+      </c>
+      <c r="H6" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" ht="15" customHeight="1">
+      <c r="B7" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" ht="15" customHeight="1">
+      <c r="B8" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" s="12">
-        <v>61.84</v>
-      </c>
-      <c r="G8" s="13">
-        <v>1.4197689569999999E-4</v>
-      </c>
-      <c r="H8" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="I8" s="14" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="I9" s="14" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="20" t="s">
+      <c r="C8" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="9">
+        <v>113.18</v>
+      </c>
+      <c r="G8" s="10">
+        <v>0.0002122129696</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" ht="15" customHeight="1">
+      <c r="B9" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="I9" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" ht="15" customHeight="1">
+      <c r="B10" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="E10" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" s="21">
-        <v>10112.396640399937</v>
-      </c>
-      <c r="G10" s="22">
-        <v>2.321679630376812E-2</v>
-      </c>
-      <c r="H10" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="20" t="s">
+      <c r="C10" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="18">
+        <v>12156.233088600042</v>
+      </c>
+      <c r="G10" s="19">
+        <v>0.02279298748106901</v>
+      </c>
+      <c r="H10" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" ht="15" customHeight="1">
+      <c r="B11" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" s="21">
-        <v>435563.82664039999</v>
-      </c>
-      <c r="G11" s="22">
-        <v>0.99999999999986811</v>
-      </c>
-      <c r="H11" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="I11" s="9" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="6" t="s">
+      <c r="C11" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="18">
+        <v>533332.1530886</v>
+      </c>
+      <c r="G11" s="19">
+        <v>0.999999999999969</v>
+      </c>
+      <c r="H11" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="2:8" ht="15" customHeight="1">
+      <c r="B14" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-    </row>
-    <row r="15" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="6" t="s">
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="20"/>
+    </row>
+    <row r="15" spans="2:8" ht="15" customHeight="1">
+      <c r="B15" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-    </row>
-    <row r="16" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="6" t="s">
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="20"/>
+    </row>
+    <row r="16" spans="2:8" ht="15" customHeight="1">
+      <c r="B16" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-    </row>
-    <row r="17" spans="2:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="4" t="s">
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20"/>
+    </row>
+    <row r="17" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B17" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
-    </row>
-    <row r="18" spans="2:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="4" t="s">
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20"/>
+      <c r="H17" s="20"/>
+    </row>
+    <row r="18" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B18" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
-      <c r="H18" s="5"/>
-    </row>
-    <row r="19" spans="2:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="4" t="s">
+      <c r="C18" s="20"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="20"/>
+      <c r="H18" s="20"/>
+    </row>
+    <row r="19" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B19" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
-    </row>
-    <row r="22" spans="2:8" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B22" s="23" t="s">
+      <c r="C19" s="20"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="20"/>
+      <c r="H19" s="20"/>
+    </row>
+    <row r="22" ht="15">
+      <c r="B22" s="20" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="37" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B37" s="23" t="s">
+    <row r="37" ht="15">
+      <c r="B37" s="20" t="s">
         <v>24</v>
-      </c>
-    </row>
-    <row r="38" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B38" s="23" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1075,7 +1123,7 @@
     <mergeCell ref="B14:H14"/>
     <mergeCell ref="B15:H15"/>
   </mergeCells>
-  <printOptions headings="1" gridLines="1"/>
+  <printOptions gridLines="1" headings="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
   <pageSetup orientation="portrait"/>
   <headerFooter alignWithMargins="0"/>
